--- a/survey_templates/035_safety_hazard_identification_quiz--survey_templates.xlsx
+++ b/survey_templates/035_safety_hazard_identification_quiz--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,10 +525,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>intro</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Intro</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>This is the beginning of the Safety Hazard Identification Quiz.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -538,43 +542,51 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>safety_hazard_questions</t>
+          <t>question_one</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>safety_hazard_questions</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Safety Hazard Recognition</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>How do you recognize safety hazards in the workplace?</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hazard_recognition</t>
+          <t>question_two</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>hazard_recognition</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Reporting Frequency</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>How often do you report safety hazards?</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>yes</t>
@@ -589,41 +601,49 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>protocols</t>
+          <t>question_three</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>protocols</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Reporting Channels</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>What channels do you use to report safety hazards?</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>reporting</t>
+          <t>question_four</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>reporting</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Near-Miss Hazards</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>How do you identify near-miss hazards?</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -635,38 +655,46 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>training</t>
+          <t>question_five</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>training</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Protocols</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>What protocols are in place for reporting safety hazards?</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>safety_committee</t>
+          <t>question_six</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>safety_committee</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Follow-up</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>How do you follow up on reported safety hazards?</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -681,15 +709,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>incident_reporting</t>
+          <t>question_seven</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>incident_reporting</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Question Seven</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>What protocols are in place for follow-up actions?</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>yes</t>
@@ -704,18 +736,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>near_miss_hazards</t>
+          <t>question_eight</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>near_miss_hazards</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Question Eight</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>How often do you follow up on reported safety hazards?</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,15 +763,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hazard_prevention</t>
+          <t>question_nine</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>hazard_prevention</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Safety Committee</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>What is your role in the safety committee?</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -745,20 +785,24 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>safety_measures</t>
+          <t>question_ten</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>safety_measures</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Question Ten</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>How do you prevent near-miss hazards?</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -773,15 +817,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>follow_up</t>
+          <t>question_eleven</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>follow_up</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Question Eleven</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>What protocols are in place for near-miss hazards?</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
@@ -791,23 +839,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>reporting_frequency</t>
+          <t>question_twelve</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>reporting_frequency</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Question Twelve</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>How do you follow up on reported safety hazards?</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -819,15 +871,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>safety_committee_roles</t>
+          <t>question_thirteen</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>safety_committee_roles</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Reporting</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>How often do you report near-miss hazards?</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>no</t>
@@ -837,20 +893,24 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>near_miss_hazards</t>
+          <t>question_fourteen</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>near_miss_hazards</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Safety Measures</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>What measures do you take to prevent safety hazards?</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
@@ -865,15 +925,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>reporting_channels</t>
+          <t>question_fifteen</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>reporting_channels</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Question Fifteen</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>What protocols are in place for reporting safety measures?</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>no</t>
@@ -888,15 +952,19 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>hazard_prevention</t>
+          <t>question_sixteen</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>hazard_prevention</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Question Sixteen</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>What channels do you use to report safety measures?</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>no</t>
@@ -906,182 +974,25 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>follow_up</t>
+          <t>question_seventeen</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>follow_up</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Question Seventeen</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>How do you follow up on reported safety measures?</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>near_miss</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>near_miss</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>follow_up</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>follow_up</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>reporting_frequency</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>reporting_frequency</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>follow_up</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>follow_up</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>follow_up</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>follow_up</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>follow_up</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>follow_up</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>follow_up</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>follow_up</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,11 +1009,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -1126,714 +1037,340 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>safety_hazard_questions_choices</t>
+          <t>question_two_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>safety_hazard_questions_choices</t>
+          <t>question_two_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>hazard_recognition_choices</t>
+          <t>question_three_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hazard_recognition_choices</t>
+          <t>question_three_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>protocols_choices</t>
+          <t>question_five_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>protocols_choices</t>
+          <t>question_five_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>reporting_choices</t>
+          <t>question_seven_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>reporting_choices</t>
+          <t>question_seven_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>training_choices</t>
+          <t>question_eight_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>training_choices</t>
+          <t>question_eight_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>safety_committee_choices</t>
+          <t>question_nine_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>safety_committee_choices</t>
+          <t>question_nine_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>incident_reporting_choices</t>
+          <t>question_eleven_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>incident_reporting_choices</t>
+          <t>question_eleven_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>near_miss_hazards_choices</t>
+          <t>question_thirteen_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>near_miss_hazards_choices</t>
+          <t>question_thirteen_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>hazard_prevention_choices</t>
+          <t>question_fifteen_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>hazard_prevention_choices</t>
+          <t>question_fifteen_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>safety_measures_choices</t>
+          <t>question_sixteen_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>safety_measures_choices</t>
+          <t>question_sixteen_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>follow_up_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>follow_up_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>reporting_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>reporting_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>safety_committee_roles_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>safety_committee_roles_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>near_miss_hazards_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>near_miss_hazards_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>reporting_channels_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>reporting_channels_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>hazard_prevention_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>hazard_prevention_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>follow_up_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>follow_up_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>follow_up_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>follow_up_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>reporting_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>reporting_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>follow_up_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>follow_up_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>follow_up_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>follow_up_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
